--- a/artfynd/A 24647-2022 artfynd.xlsx
+++ b/artfynd/A 24647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY10"/>
+  <dimension ref="A1:AY11"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1852,6 +1852,137 @@
       </c>
       <c r="AY10" t="inlineStr"/>
     </row>
+    <row r="11">
+      <c r="A11" t="n">
+        <v>82451253</v>
+      </c>
+      <c r="B11" t="n">
+        <v>56159</v>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>Ovaliderad</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E11" t="n">
+        <v>206000</v>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>Gråskimlig fladdermus</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>Vespertilio murinus</t>
+        </is>
+      </c>
+      <c r="H11" t="inlineStr">
+        <is>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I11" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J11" t="inlineStr">
+        <is>
+          <t>registreringar</t>
+        </is>
+      </c>
+      <c r="M11" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>autobox med höghastighetsinspelning</t>
+        </is>
+      </c>
+      <c r="P11" t="inlineStr">
+        <is>
+          <t>Hässleholm-Lund, Sk</t>
+        </is>
+      </c>
+      <c r="Q11" t="n">
+        <v>411458</v>
+      </c>
+      <c r="R11" t="n">
+        <v>6196421</v>
+      </c>
+      <c r="S11" t="n">
+        <v>25</v>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="U11" t="inlineStr">
+        <is>
+          <t>Hörby</t>
+        </is>
+      </c>
+      <c r="V11" t="inlineStr">
+        <is>
+          <t>Skåne</t>
+        </is>
+      </c>
+      <c r="W11" t="inlineStr">
+        <is>
+          <t>Fulltofta</t>
+        </is>
+      </c>
+      <c r="Y11" t="inlineStr">
+        <is>
+          <t>2019-07-31</t>
+        </is>
+      </c>
+      <c r="Z11" t="inlineStr">
+        <is>
+          <t>21:00</t>
+        </is>
+      </c>
+      <c r="AA11" t="inlineStr">
+        <is>
+          <t>2019-08-01</t>
+        </is>
+      </c>
+      <c r="AB11" t="inlineStr">
+        <is>
+          <t>05:00</t>
+        </is>
+      </c>
+      <c r="AD11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG11" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT11" t="inlineStr"/>
+      <c r="AW11" t="inlineStr">
+        <is>
+          <t>Martin Brüsin</t>
+        </is>
+      </c>
+      <c r="AX11" t="inlineStr">
+        <is>
+          <t>Martin Brüsin, Alexander Eriksson</t>
+        </is>
+      </c>
+      <c r="AY11" t="inlineStr"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/A 24647-2022 artfynd.xlsx
+++ b/artfynd/A 24647-2022 artfynd.xlsx
@@ -529,7 +529,7 @@
       </c>
       <c r="W1" t="inlineStr">
         <is>
-          <t>Församling</t>
+          <t>Socken</t>
         </is>
       </c>
       <c r="X1" t="inlineStr">

--- a/artfynd/A 24647-2022 artfynd.xlsx
+++ b/artfynd/A 24647-2022 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY17"/>
+  <dimension ref="A1:AZ17"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -798,6 +803,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456324</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -924,6 +934,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82447824</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -1050,6 +1065,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456783</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1176,6 +1196,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456784</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1302,6 +1327,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456220</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1428,6 +1458,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456221</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1554,6 +1589,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82455965</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1680,6 +1720,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82455966</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1806,6 +1851,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82456268</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1932,6 +1982,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82449899</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -2058,6 +2113,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82449900</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -2184,6 +2244,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82453816</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2310,6 +2375,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82453817</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2436,6 +2506,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82451252</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2562,6 +2637,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82451253</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2688,8 +2768,31 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/82451076</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>